--- a/reference_materials/도면_정답지.xlsx
+++ b/reference_materials/도면_정답지.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lang0\projects\construction-ai-estimator\reference_materials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_2025-26\aiffel_p\c_partner\steel-qto\reference_materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45C8825-0590-46A3-9AB0-392FF91B732A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDD54BE-63C4-44AE-8FBE-68E24A3BAE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="684" windowWidth="16416" windowHeight="11820" tabRatio="500" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="도면1-기둥" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="도면5-기둥" sheetId="9" r:id="rId9"/>
     <sheet name="도면5-보" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,6 +36,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -1675,7 +1678,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1692,6 +1695,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1722,7 +1731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1747,6 +1756,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2013,7 +2025,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2044,7 +2056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="17">
+    <row r="2" spans="1:7" ht="17.399999999999999">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -2064,7 +2076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="17">
+    <row r="3" spans="1:7" ht="17.399999999999999">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -2082,7 +2094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="17">
+    <row r="4" spans="1:7" ht="17.399999999999999">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -2102,7 +2114,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17">
+    <row r="5" spans="1:7" ht="17.399999999999999">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -2120,7 +2132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="17">
+    <row r="6" spans="1:7" ht="17.399999999999999">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -2136,7 +2148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17">
+    <row r="7" spans="1:7" ht="17.399999999999999">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -2152,7 +2164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="17">
+    <row r="8" spans="1:7" ht="17.399999999999999">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
@@ -2168,7 +2180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="17">
+    <row r="9" spans="1:7" ht="17.399999999999999">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
@@ -2184,31 +2196,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="17">
+    <row r="10" spans="1:7" ht="17.399999999999999">
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="9">
         <v>15</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="9">
         <v>4</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="9">
         <v>2</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="9">
         <v>4</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="9">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="17">
+    <row r="11" spans="1:7" ht="17.399999999999999">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -2232,7 +2244,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="17">
+    <row r="12" spans="1:7" ht="17.399999999999999">
       <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
@@ -2246,7 +2258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="17">
+    <row r="13" spans="1:7" ht="17.399999999999999">
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
@@ -2262,7 +2274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="17">
+    <row r="14" spans="1:7" ht="17.399999999999999">
       <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
@@ -2276,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="17">
+    <row r="15" spans="1:7" ht="17.399999999999999">
       <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
@@ -2290,7 +2302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="31">
+    <row r="16" spans="1:7" ht="31.2">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -2306,7 +2318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="31">
+    <row r="17" spans="1:7" ht="31.2">
       <c r="A17" s="3" t="s">
         <v>27</v>
       </c>
@@ -2322,7 +2334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="17">
+    <row r="18" spans="1:7" ht="17.399999999999999">
       <c r="A18" s="6" t="s">
         <v>6</v>
       </c>
@@ -2358,7 +2370,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2413,7 +2425,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="17">
+    <row r="2" spans="1:15" ht="17.399999999999999">
       <c r="A2" s="5" t="s">
         <v>81</v>
       </c>
@@ -2437,7 +2449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="17">
+    <row r="3" spans="1:15" ht="17.399999999999999">
       <c r="A3" s="5" t="s">
         <v>82</v>
       </c>
@@ -2461,7 +2473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="17">
+    <row r="4" spans="1:15" ht="17.399999999999999">
       <c r="A4" s="5" t="s">
         <v>83</v>
       </c>
@@ -2485,7 +2497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="17">
+    <row r="5" spans="1:15" ht="17.399999999999999">
       <c r="A5" s="5" t="s">
         <v>84</v>
       </c>
@@ -2517,7 +2529,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="17">
+    <row r="6" spans="1:15" ht="17.399999999999999">
       <c r="A6" s="3" t="s">
         <v>56</v>
       </c>
@@ -2557,7 +2569,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="17">
+    <row r="7" spans="1:15" ht="17.399999999999999">
       <c r="A7" s="3" t="s">
         <v>54</v>
       </c>
@@ -2581,7 +2593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="17">
+    <row r="8" spans="1:15" ht="17.399999999999999">
       <c r="A8" s="3" t="s">
         <v>85</v>
       </c>
@@ -2611,7 +2623,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="17">
+    <row r="9" spans="1:15" ht="17.399999999999999">
       <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
@@ -2679,7 +2691,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2743,7 +2755,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="17">
+    <row r="2" spans="1:18" ht="17.399999999999999">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -2770,7 +2782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17">
+    <row r="3" spans="1:18" ht="17.399999999999999">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -2797,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17">
+    <row r="4" spans="1:18" ht="17.399999999999999">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -2824,7 +2836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17">
+    <row r="5" spans="1:18" ht="17.399999999999999">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -2851,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17">
+    <row r="6" spans="1:18" ht="17.399999999999999">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -2878,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17">
+    <row r="7" spans="1:18" ht="17.399999999999999">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -2917,7 +2929,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17">
+    <row r="8" spans="1:18" ht="17.399999999999999">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
@@ -2956,7 +2968,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17">
+    <row r="9" spans="1:18" ht="17.399999999999999">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
@@ -2995,7 +3007,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17">
+    <row r="10" spans="1:18" ht="17.399999999999999">
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
@@ -3022,7 +3034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17">
+    <row r="11" spans="1:18" ht="17.399999999999999">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -3049,7 +3061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17">
+    <row r="12" spans="1:18" ht="17.399999999999999">
       <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
@@ -3074,7 +3086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17">
+    <row r="13" spans="1:18" ht="17.399999999999999">
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
@@ -3101,7 +3113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17">
+    <row r="14" spans="1:18" ht="17.399999999999999">
       <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
@@ -3126,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17">
+    <row r="15" spans="1:18" ht="17.399999999999999">
       <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
@@ -3157,7 +3169,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="31">
+    <row r="16" spans="1:18" ht="31.2">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -3186,7 +3198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="31">
+    <row r="17" spans="1:18" ht="31.2">
       <c r="A17" s="3" t="s">
         <v>27</v>
       </c>
@@ -3217,7 +3229,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17">
+    <row r="18" spans="1:18" ht="17.399999999999999">
       <c r="A18" s="6" t="s">
         <v>6</v>
       </c>
@@ -3297,7 +3309,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3331,7 +3343,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="34">
+    <row r="2" spans="1:8" ht="34.799999999999997">
       <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
@@ -3346,7 +3358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="17">
+    <row r="3" spans="1:8" ht="17.399999999999999">
       <c r="A3" s="5" t="s">
         <v>45</v>
       </c>
@@ -3363,7 +3375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="17">
+    <row r="4" spans="1:8" ht="17.399999999999999">
       <c r="A4" s="5" t="s">
         <v>47</v>
       </c>
@@ -3380,7 +3392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="17">
+    <row r="5" spans="1:8" ht="17.399999999999999">
       <c r="A5" s="8" t="s">
         <v>91</v>
       </c>
@@ -3390,18 +3402,18 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="4">
+      <c r="F5" s="9">
         <v>10</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="9">
         <v>4</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="9">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="17">
+    <row r="6" spans="1:8" ht="17.399999999999999">
       <c r="A6" s="8" t="s">
         <v>92</v>
       </c>
@@ -3416,7 +3428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="17">
+    <row r="7" spans="1:8" ht="17.399999999999999">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -3456,7 +3468,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3487,7 +3499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="34">
+    <row r="2" spans="1:7" ht="34.799999999999997">
       <c r="A2" s="8" t="s">
         <v>93</v>
       </c>
@@ -3501,7 +3513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="17">
+    <row r="3" spans="1:7" ht="17.399999999999999">
       <c r="A3" s="5" t="s">
         <v>45</v>
       </c>
@@ -3517,7 +3529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="17">
+    <row r="4" spans="1:7" ht="17.399999999999999">
       <c r="A4" s="5" t="s">
         <v>47</v>
       </c>
@@ -3533,7 +3545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17">
+    <row r="5" spans="1:7" ht="17.399999999999999">
       <c r="A5" s="8" t="s">
         <v>91</v>
       </c>
@@ -3549,7 +3561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="17">
+    <row r="6" spans="1:7" ht="17.399999999999999">
       <c r="A6" s="8" t="s">
         <v>92</v>
       </c>
@@ -3573,7 +3585,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17">
+    <row r="7" spans="1:7" ht="17.399999999999999">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -3609,7 +3621,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3640,31 +3652,31 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="17">
+    <row r="2" spans="1:7" ht="17.399999999999999">
       <c r="A2" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="9">
         <v>8</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="9">
         <v>15</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="9">
         <v>8</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="9">
         <v>1</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="9">
         <f t="shared" ref="G2:G8" si="0">SUM(C2:F2)</f>
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="17">
+    <row r="3" spans="1:7" ht="17.399999999999999">
       <c r="A3" s="3" t="s">
         <v>56</v>
       </c>
@@ -3680,7 +3692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="17">
+    <row r="4" spans="1:7" ht="17.399999999999999">
       <c r="A4" s="5" t="s">
         <v>57</v>
       </c>
@@ -3696,7 +3708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17">
+    <row r="5" spans="1:7" ht="17.399999999999999">
       <c r="A5" s="5" t="s">
         <v>58</v>
       </c>
@@ -3712,7 +3724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="17">
+    <row r="6" spans="1:7" ht="17.399999999999999">
       <c r="A6" s="5" t="s">
         <v>59</v>
       </c>
@@ -3728,7 +3740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17">
+    <row r="7" spans="1:7" ht="17.399999999999999">
       <c r="A7" s="5" t="s">
         <v>60</v>
       </c>
@@ -3744,7 +3756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="17">
+    <row r="8" spans="1:7" ht="17.399999999999999">
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
@@ -3780,7 +3792,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:T8"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3850,7 +3862,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="17">
+    <row r="2" spans="1:20" ht="17.399999999999999">
       <c r="A2" s="3" t="s">
         <v>54</v>
       </c>
@@ -3879,7 +3891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="17">
+    <row r="3" spans="1:20" ht="17.399999999999999">
       <c r="A3" s="3" t="s">
         <v>56</v>
       </c>
@@ -3930,7 +3942,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="17">
+    <row r="4" spans="1:20" ht="17.399999999999999">
       <c r="A4" s="5" t="s">
         <v>57</v>
       </c>
@@ -3973,7 +3985,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="17">
+    <row r="5" spans="1:20" ht="17.399999999999999">
       <c r="A5" s="5" t="s">
         <v>58</v>
       </c>
@@ -4010,7 +4022,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17">
+    <row r="6" spans="1:20" ht="17.399999999999999">
       <c r="A6" s="5" t="s">
         <v>59</v>
       </c>
@@ -4039,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17">
+    <row r="7" spans="1:20" ht="17.399999999999999">
       <c r="A7" s="5" t="s">
         <v>60</v>
       </c>
@@ -4068,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="17">
+    <row r="8" spans="1:20" ht="17.399999999999999">
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
@@ -4156,7 +4168,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -4190,7 +4202,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="17">
+    <row r="2" spans="1:8" ht="17.399999999999999">
       <c r="A2" s="3" t="s">
         <v>80</v>
       </c>
@@ -4200,18 +4212,18 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="4">
+      <c r="F2" s="9">
         <v>14</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="9">
         <v>4</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="9">
         <f>SUM(C2:G2)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="17">
+    <row r="3" spans="1:8" ht="17.399999999999999">
       <c r="A3" s="5" t="s">
         <v>58</v>
       </c>
@@ -4232,7 +4244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="17">
+    <row r="4" spans="1:8" ht="17.399999999999999">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -4272,7 +4284,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -4303,7 +4315,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="17">
+    <row r="2" spans="1:7" ht="17.399999999999999">
       <c r="A2" s="3" t="s">
         <v>80</v>
       </c>
@@ -4319,7 +4331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="17">
+    <row r="3" spans="1:7" ht="17.399999999999999">
       <c r="A3" s="5" t="s">
         <v>58</v>
       </c>
@@ -4339,7 +4351,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="17">
+    <row r="4" spans="1:7" ht="17.399999999999999">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -4375,7 +4387,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -4406,7 +4418,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="17">
+    <row r="2" spans="1:7" ht="17.399999999999999">
       <c r="A2" s="5" t="s">
         <v>81</v>
       </c>
@@ -4422,7 +4434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="17">
+    <row r="3" spans="1:7" ht="17.399999999999999">
       <c r="A3" s="5" t="s">
         <v>82</v>
       </c>
@@ -4438,7 +4450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="17">
+    <row r="4" spans="1:7" ht="17.399999999999999">
       <c r="A4" s="5" t="s">
         <v>83</v>
       </c>
@@ -4454,7 +4466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17">
+    <row r="5" spans="1:7" ht="17.399999999999999">
       <c r="A5" s="5" t="s">
         <v>84</v>
       </c>
@@ -4470,7 +4482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="17">
+    <row r="6" spans="1:7" ht="17.399999999999999">
       <c r="A6" s="3" t="s">
         <v>56</v>
       </c>
@@ -4486,31 +4498,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17">
+    <row r="7" spans="1:7" ht="17.399999999999999">
       <c r="A7" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="9">
         <v>2</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="9">
         <v>4</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="9">
         <v>8</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="9">
         <v>6</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="9">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="17">
+    <row r="8" spans="1:7" ht="17.399999999999999">
       <c r="A8" s="3" t="s">
         <v>85</v>
       </c>
@@ -4526,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="17">
+    <row r="9" spans="1:7" ht="17.399999999999999">
       <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
